--- a/output/pdf_financials_xlsx/SGU.xlsx
+++ b/output/pdf_financials_xlsx/SGU.xlsx
@@ -960,10 +960,10 @@
         <v>0</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.003841</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.022949</v>
       </c>
     </row>
     <row r="13">
@@ -1748,10 +1748,10 @@
         <v>-1.139163</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-2.82292</v>
+        <v>-2.826761</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-3.118777</v>
+        <v>-3.141726</v>
       </c>
     </row>
     <row r="28">
@@ -1844,10 +1844,10 @@
         <v>-1.139163</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-2.82292</v>
+        <v>-2.826761</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-3.118777</v>
+        <v>-3.141726</v>
       </c>
     </row>
     <row r="30">
@@ -2056,43 +2056,43 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.130343</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.010167</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.04521</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.050568</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.27018</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.461921</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.267639</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.462184</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.075281</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.003219</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.121179</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.090488</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>3.372744</v>
       </c>
     </row>
     <row r="35">
@@ -2148,43 +2148,43 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.02</v>
+        <v>0.150343</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.080167</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.04521</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.3</v>
+        <v>0.350568</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.27018</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.461921</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.267639</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.462184</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.075281</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.003219</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.121179</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.090488</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>3.372744</v>
       </c>
     </row>
     <row r="37">
@@ -2700,43 +2700,43 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.13401</v>
+        <v>0.003667</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.013834</v>
+        <v>0.003667</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.053736</v>
+        <v>0.008526000000000001</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.09550400000000001</v>
+        <v>0.044936</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.313888</v>
+        <v>0.043708</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.4963</v>
+        <v>0.034379</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.307783</v>
+        <v>0.040144</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.48487</v>
+        <v>0.022686</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.492587</v>
+        <v>1.417306</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.132897</v>
+        <v>0.129678</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.174333</v>
+        <v>0.053154</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.610561</v>
+        <v>0.520073</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>3.467215</v>
+        <v>0.094471</v>
       </c>
     </row>
     <row r="49">
@@ -6981,7 +6981,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -21835,7 +21835,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -23324,7 +23324,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">

--- a/output/pdf_financials_xlsx/SGU.xlsx
+++ b/output/pdf_financials_xlsx/SGU.xlsx
@@ -3486,19 +3486,19 @@
         <v>0</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>0.374114</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>0.491588</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>0.130065</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>0.319004</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>0.774259</v>
       </c>
     </row>
     <row r="65">
@@ -5594,22 +5594,22 @@
         <v>0</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.007303</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.007542</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.007786</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>0.00804</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>0.0083</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>0.008569999999999999</v>
       </c>
       <c r="I110" s="1" t="inlineStr">
         <is>
@@ -11469,7 +11469,11 @@
           <t>Proceeds from private placement 8</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>-</t>
@@ -14560,7 +14564,11 @@
           <t>Finders' warrants issued in connection with private placement 8 $</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
@@ -15198,7 +15206,11 @@
           <t>Finder’s warrants issued in connection with private placement 8</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
           <t>-</t>
@@ -15279,7 +15291,11 @@
           <t>Accretion expense 9</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>-</t>
@@ -15680,7 +15696,11 @@
           <t>Shares to be issued related to private placement 7</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
           <t>-</t>
@@ -15761,7 +15781,11 @@
           <t>Proceeds from private placement 7</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>-</t>
@@ -16966,7 +16990,11 @@
           <t>Accretion expense (Note 9)</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
@@ -17363,7 +17391,11 @@
           <t>Shares to be issued related to private placement (Note 7)</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
@@ -17444,7 +17476,11 @@
           <t>Proceeds from private placement (Note 7)</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
@@ -18398,7 +18434,11 @@
           <t>Accretion expense (Note 10)</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
           <t>-</t>
@@ -18633,7 +18673,11 @@
           <t>Shares to be issued related to private placement (Note 8)</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>
@@ -18714,7 +18758,11 @@
           <t>Proceeds from private placement (Note 8)</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>
@@ -20004,7 +20052,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E169" t="inlineStr">
         <is>
           <t>-</t>
